--- a/MAJSushiConfig/ig/StructureDefinition-fr-medication-dispense-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-medication-dispense-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-dispense-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-dispense-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -605,7 +605,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-document|0.1.0)</t>
+Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-document|0.1.0)</t>
   </si>
   <si>
     <t>Médicament délivré</t>
@@ -688,7 +688,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
 </t>
   </si>
   <si>
@@ -827,7 +827,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-request-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-request-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1042,7 +1042,7 @@
     <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-edqm-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-edqm-document|0.1.0</t>
   </si>
   <si>
     <t>Quantity.unit</t>
@@ -2111,7 +2111,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="105.6640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="102.46484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2126,7 +2126,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.7734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.53515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="73.9609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
